--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755175568_h_11.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755175568_h_11.xlsx
@@ -658,7 +658,7 @@
         <v>0.008452553723509622</v>
       </c>
       <c r="C2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>48234348</v>
+        <v>4006375</v>
       </c>
       <c r="L2" t="n">
-        <v>25153906</v>
+        <v>1653824</v>
       </c>
       <c r="M2" t="n">
-        <v>5863794</v>
+        <v>314123</v>
       </c>
       <c r="N2" t="n">
-        <v>245024</v>
+        <v>6638</v>
       </c>
       <c r="O2" t="n">
-        <v>3488969</v>
+        <v>184537</v>
       </c>
       <c r="P2" t="n">
-        <v>1293362</v>
+        <v>53227</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999732375144958</v>
+        <v>0.9999473690986633</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8319105505943298</v>
+        <v>0.7186760902404785</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7050057053565979</v>
+        <v>0.5340784192085266</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6297794580459595</v>
+        <v>0.4020367860794067</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2386192232370377</v>
+        <v>0.05640960112214088</v>
       </c>
       <c r="V2" t="n">
-        <v>0.677367091178894</v>
+        <v>0.4501901566982269</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8002289533615112</v>
+        <v>0.5972576141357422</v>
       </c>
       <c r="X2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>53079081</v>
+        <v>4775969</v>
       </c>
       <c r="AG2" t="n">
-        <v>33018842</v>
+        <v>3037162</v>
       </c>
       <c r="AH2" t="n">
-        <v>8835934</v>
+        <v>808667</v>
       </c>
       <c r="AI2" t="n">
-        <v>651291</v>
+        <v>59431</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5060281</v>
+        <v>461766</v>
       </c>
       <c r="AK2" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9559435248374939</v>
+        <v>0.9546229243278503</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9116207361221313</v>
+        <v>0.912503182888031</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580287098884583</v>
+        <v>0.8579802513122559</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6615698337554932</v>
+        <v>0.6605058908462524</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.901967465877533</v>
+        <v>0.9019959568977356</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314546585083008</v>
+        <v>0.9314878582954407</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002025028638077513</v>
       </c>
       <c r="C3" t="n">
-        <v>1000</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
-        <v>48234348</v>
+        <v>4006375</v>
       </c>
       <c r="E3" t="n">
-        <v>6955107</v>
+        <v>930129</v>
       </c>
       <c r="F3" t="n">
-        <v>211224</v>
+        <v>44188</v>
       </c>
       <c r="G3" t="n">
-        <v>16985</v>
+        <v>3528</v>
       </c>
       <c r="H3" t="n">
-        <v>14898</v>
+        <v>4082</v>
       </c>
       <c r="I3" t="n">
-        <v>1015</v>
+        <v>379</v>
       </c>
       <c r="J3" t="n">
-        <v>110763952</v>
+        <v>10069286</v>
       </c>
       <c r="K3" t="n">
-        <v>115395560</v>
+        <v>9859001</v>
       </c>
       <c r="L3" t="n">
-        <v>133757669</v>
+        <v>11633324</v>
       </c>
       <c r="M3" t="n">
-        <v>166819067</v>
+        <v>15004411</v>
       </c>
       <c r="N3" t="n">
-        <v>178808728</v>
+        <v>16214856</v>
       </c>
       <c r="O3" t="n">
-        <v>173300030</v>
+        <v>15678050</v>
       </c>
       <c r="P3" t="n">
-        <v>178124577</v>
+        <v>16186176</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8701130151748657</v>
+        <v>0.8030877113342285</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6930744051933289</v>
+        <v>0.4951708316802979</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5687560439109802</v>
+        <v>0.3326224684715271</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2486404776573181</v>
+        <v>0.073667973279953</v>
       </c>
       <c r="V3" t="n">
-        <v>0.621458888053894</v>
+        <v>0.3600173890590668</v>
       </c>
       <c r="W3" t="n">
-        <v>0.607627272605896</v>
+        <v>0.2744621932506561</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>53079081</v>
+        <v>4775969</v>
       </c>
       <c r="Z3" t="n">
-        <v>2185497</v>
+        <v>197364</v>
       </c>
       <c r="AA3" t="n">
-        <v>93996</v>
+        <v>8471</v>
       </c>
       <c r="AB3" t="n">
-        <v>75314</v>
+        <v>6869</v>
       </c>
       <c r="AC3" t="n">
-        <v>359</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>330</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>110765820</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>122695174</v>
+        <v>11200265</v>
       </c>
       <c r="AG3" t="n">
-        <v>141081682</v>
+        <v>12784871</v>
       </c>
       <c r="AH3" t="n">
-        <v>168804129</v>
+        <v>15337760</v>
       </c>
       <c r="AI3" t="n">
-        <v>179257373</v>
+        <v>16295346</v>
       </c>
       <c r="AJ3" t="n">
-        <v>174411852</v>
+        <v>15853250</v>
       </c>
       <c r="AK3" t="n">
-        <v>178301599</v>
+        <v>16208790</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575085639953613</v>
+        <v>0.957354724407196</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097797274589539</v>
+        <v>0.9093555212020874</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8570374250411987</v>
+        <v>0.8562913537025452</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6609038710594177</v>
+        <v>0.6595603227615356</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013426303863525</v>
+        <v>0.9008697271347046</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311618804931641</v>
+        <v>0.9308778047561646</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03196808737360584</v>
       </c>
       <c r="C4" t="n">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="D4" t="n">
-        <v>8979008</v>
+        <v>1400230</v>
       </c>
       <c r="E4" t="n">
-        <v>25153906</v>
+        <v>1653824</v>
       </c>
       <c r="F4" t="n">
-        <v>1827957</v>
+        <v>225682</v>
       </c>
       <c r="G4" t="n">
-        <v>104154</v>
+        <v>18833</v>
       </c>
       <c r="H4" t="n">
-        <v>208631</v>
+        <v>37163</v>
       </c>
       <c r="I4" t="n">
-        <v>19410</v>
+        <v>4066</v>
       </c>
       <c r="J4" t="n">
-        <v>1868</v>
+        <v>334</v>
       </c>
       <c r="K4" t="n">
-        <v>9745863</v>
+        <v>1568285</v>
       </c>
       <c r="L4" t="n">
-        <v>10525105</v>
+        <v>1442770</v>
       </c>
       <c r="M4" t="n">
-        <v>3447075</v>
+        <v>467206</v>
       </c>
       <c r="N4" t="n">
-        <v>781817</v>
+        <v>111037</v>
       </c>
       <c r="O4" t="n">
-        <v>1661811</v>
+        <v>225372</v>
       </c>
       <c r="P4" t="n">
-        <v>322878</v>
+        <v>35892</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999865889549255</v>
+        <v>0.9999737143516541</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8505830764770508</v>
+        <v>0.7585407495498657</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6989891529083252</v>
+        <v>0.5138892531394958</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5977142453193665</v>
+        <v>0.3640502989292145</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2435268014669418</v>
+        <v>0.06389389187097549</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6482096910476685</v>
+        <v>0.400085836648941</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6907536387443542</v>
+        <v>0.3760947585105896</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2284621</v>
+        <v>212190</v>
       </c>
       <c r="Z4" t="n">
-        <v>33018842</v>
+        <v>3037162</v>
       </c>
       <c r="AA4" t="n">
-        <v>915390</v>
+        <v>83722</v>
       </c>
       <c r="AB4" t="n">
-        <v>61077</v>
+        <v>5633</v>
       </c>
       <c r="AC4" t="n">
-        <v>12548</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>748</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2446249</v>
+        <v>227021</v>
       </c>
       <c r="AG4" t="n">
-        <v>3201092</v>
+        <v>291223</v>
       </c>
       <c r="AH4" t="n">
-        <v>1462013</v>
+        <v>133857</v>
       </c>
       <c r="AI4" t="n">
-        <v>333172</v>
+        <v>30547</v>
       </c>
       <c r="AJ4" t="n">
-        <v>549989</v>
+        <v>50172</v>
       </c>
       <c r="AK4" t="n">
-        <v>145856</v>
+        <v>13278</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567253589630127</v>
+        <v>0.9559868574142456</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106993675231934</v>
+        <v>0.9109266996383667</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8575327396392822</v>
+        <v>0.857134997844696</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6612366437911987</v>
+        <v>0.6600327491760254</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016548991203308</v>
+        <v>0.9014324545860291</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313082695007324</v>
+        <v>0.9311826825141907</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>216</v>
+        <v>28</v>
       </c>
       <c r="D5" t="n">
-        <v>549642</v>
+        <v>124228</v>
       </c>
       <c r="E5" t="n">
-        <v>2888753</v>
+        <v>381110</v>
       </c>
       <c r="F5" t="n">
-        <v>5863794</v>
+        <v>314123</v>
       </c>
       <c r="G5" t="n">
-        <v>250517</v>
+        <v>31964</v>
       </c>
       <c r="H5" t="n">
-        <v>686718</v>
+        <v>82156</v>
       </c>
       <c r="I5" t="n">
-        <v>70218</v>
+        <v>10774</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7200229</v>
+        <v>982339</v>
       </c>
       <c r="L5" t="n">
-        <v>11139320</v>
+        <v>1686082</v>
       </c>
       <c r="M5" t="n">
-        <v>4446064</v>
+        <v>630260</v>
       </c>
       <c r="N5" t="n">
-        <v>740431</v>
+        <v>83469</v>
       </c>
       <c r="O5" t="n">
-        <v>2125190</v>
+        <v>328041</v>
       </c>
       <c r="P5" t="n">
-        <v>835183</v>
+        <v>140705</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999896287918091</v>
+        <v>0.9999796748161316</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9061553478240967</v>
+        <v>0.84462571144104</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8800259828567505</v>
+        <v>0.8094022870063782</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9562891125679016</v>
+        <v>0.9331465363502502</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9915700554847717</v>
+        <v>0.9881514310836792</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9790282249450684</v>
+        <v>0.9662882089614868</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9935868382453918</v>
+        <v>0.9892423748970032</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>89118</v>
+        <v>8164</v>
       </c>
       <c r="Z5" t="n">
-        <v>946597</v>
+        <v>87570</v>
       </c>
       <c r="AA5" t="n">
-        <v>8835934</v>
+        <v>808667</v>
       </c>
       <c r="AB5" t="n">
-        <v>109931</v>
+        <v>10048</v>
       </c>
       <c r="AC5" t="n">
-        <v>321315</v>
+        <v>29301</v>
       </c>
       <c r="AD5" t="n">
-        <v>6963</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2355496</v>
+        <v>212745</v>
       </c>
       <c r="AG5" t="n">
-        <v>3274384</v>
+        <v>302744</v>
       </c>
       <c r="AH5" t="n">
-        <v>1473924</v>
+        <v>135716</v>
       </c>
       <c r="AI5" t="n">
-        <v>334164</v>
+        <v>30676</v>
       </c>
       <c r="AJ5" t="n">
-        <v>553878</v>
+        <v>50812</v>
       </c>
       <c r="AK5" t="n">
-        <v>146525</v>
+        <v>13405</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734087586402893</v>
+        <v>0.9732111096382141</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641398787498474</v>
+        <v>0.9638177752494812</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.983741283416748</v>
+        <v>0.983578622341156</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963043928146362</v>
+        <v>0.9962705373764038</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938869476318359</v>
+        <v>0.993848443031311</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983808398246765</v>
+        <v>0.9983745813369751</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>144</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>160490</v>
+        <v>23606</v>
       </c>
       <c r="E6" t="n">
-        <v>215906</v>
+        <v>26158</v>
       </c>
       <c r="F6" t="n">
-        <v>252550</v>
+        <v>23716</v>
       </c>
       <c r="G6" t="n">
-        <v>245024</v>
+        <v>6638</v>
       </c>
       <c r="H6" t="n">
-        <v>101753</v>
+        <v>8902</v>
       </c>
       <c r="I6" t="n">
-        <v>9588</v>
+        <v>1070</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>71955</v>
+        <v>6631</v>
       </c>
       <c r="Z6" t="n">
-        <v>59191</v>
+        <v>5398</v>
       </c>
       <c r="AA6" t="n">
-        <v>120711</v>
+        <v>11132</v>
       </c>
       <c r="AB6" t="n">
-        <v>651291</v>
+        <v>59431</v>
       </c>
       <c r="AC6" t="n">
-        <v>77015</v>
+        <v>7033</v>
       </c>
       <c r="AD6" t="n">
-        <v>5292</v>
+        <v>482</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="D7" t="n">
-        <v>53151</v>
+        <v>18380</v>
       </c>
       <c r="E7" t="n">
-        <v>424497</v>
+        <v>94065</v>
       </c>
       <c r="F7" t="n">
-        <v>1060105</v>
+        <v>149945</v>
       </c>
       <c r="G7" t="n">
-        <v>364706</v>
+        <v>46010</v>
       </c>
       <c r="H7" t="n">
-        <v>3488969</v>
+        <v>184537</v>
       </c>
       <c r="I7" t="n">
-        <v>222647</v>
+        <v>19603</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>247</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8916</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>328269</v>
+        <v>30199</v>
       </c>
       <c r="AB7" t="n">
-        <v>83923</v>
+        <v>7730</v>
       </c>
       <c r="AC7" t="n">
-        <v>5060281</v>
+        <v>461766</v>
       </c>
       <c r="AD7" t="n">
-        <v>132523</v>
+        <v>12065</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>264</v>
+        <v>110</v>
       </c>
       <c r="D8" t="n">
-        <v>3572</v>
+        <v>1841</v>
       </c>
       <c r="E8" t="n">
-        <v>40842</v>
+        <v>11308</v>
       </c>
       <c r="F8" t="n">
-        <v>95239</v>
+        <v>23675</v>
       </c>
       <c r="G8" t="n">
-        <v>45455</v>
+        <v>10702</v>
       </c>
       <c r="H8" t="n">
-        <v>649811</v>
+        <v>93069</v>
       </c>
       <c r="I8" t="n">
-        <v>1293362</v>
+        <v>53227</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>308</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>891</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3647</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2927</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>138752</v>
+        <v>12696</v>
       </c>
       <c r="AD8" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
